--- a/docs/MOPED_II_Mapping.xlsx
+++ b/docs/MOPED_II_Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/work/GitHub/ELGA-MOPED-R5/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF804053-FEAF-FD40-8B3D-53A2FD4E603E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9D29DA-BFCF-C94F-BE41-C04E4F35D7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1000" windowWidth="30240" windowHeight="17960" firstSheet="5" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17940" firstSheet="5" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="X01" sheetId="1" r:id="rId1"/>

--- a/docs/MOPED_II_Mapping.xlsx
+++ b/docs/MOPED_II_Mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/work/GitHub/ELGA-MOPED-R5/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9D29DA-BFCF-C94F-BE41-C04E4F35D7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{978D49B1-85C7-AA4D-8FF5-EF9E04AF7686}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17940" firstSheet="5" activeTab="16" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17940" firstSheet="5" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="X01" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6946" uniqueCount="898">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6991" uniqueCount="900">
   <si>
     <t>Basisdaten zum stationären Aufenthalt/
 ambulanten Besuch</t>
@@ -2303,9 +2303,6 @@
     <t>noch notwendig?</t>
   </si>
   <si>
-    <t>erst in K05 relevant</t>
-  </si>
-  <si>
     <t>MopedComposition</t>
   </si>
   <si>
@@ -2949,10 +2946,20 @@
     <t>*zwingend wenn bekannt</t>
   </si>
   <si>
-    <t>Z</t>
-  </si>
-  <si>
     <t>Kardinalität LKF</t>
+  </si>
+  <si>
+    <t>nicht mehr Tel der KaOrg (Stand 2026)</t>
+  </si>
+  <si>
+    <t>*zwingend wenn zutreffend; TBD: Wenn Rückmeldung „in Bearbeitung“ (VAEST = 18 oder 98)
+dann nicht zwingend</t>
+  </si>
+  <si>
+    <t>in K01 bereits zwingend daher für K05 nicht mehr optional notwendig</t>
+  </si>
+  <si>
+    <t>*in Zukunft immer codiert notwendig?</t>
   </si>
 </sst>
 </file>
@@ -3279,7 +3286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -3372,6 +3379,9 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -3389,10 +3399,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3941,10 +3947,10 @@
         <v>24</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6" t="s">
@@ -4008,10 +4014,10 @@
         <v>24</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
@@ -4075,10 +4081,10 @@
         <v>24</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
@@ -4140,10 +4146,10 @@
         <v>24</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
@@ -4203,10 +4209,10 @@
         <v>24</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
@@ -4266,10 +4272,10 @@
         <v>24</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
@@ -4325,16 +4331,16 @@
         <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="F10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
@@ -4344,7 +4350,7 @@
         <v>7</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L10" s="6" t="s">
         <v>496</v>
@@ -4392,10 +4398,10 @@
         <v>24</v>
       </c>
       <c r="F11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6" t="s">
@@ -4455,10 +4461,10 @@
         <v>24</v>
       </c>
       <c r="F12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
@@ -4468,7 +4474,7 @@
         <v>9</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L12" s="6" t="s">
         <v>496</v>
@@ -4516,10 +4522,10 @@
         <v>24</v>
       </c>
       <c r="F13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
@@ -4529,7 +4535,7 @@
         <v>10</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L13" s="6" t="s">
         <v>496</v>
@@ -4577,10 +4583,10 @@
         <v>24</v>
       </c>
       <c r="F14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
@@ -4590,7 +4596,7 @@
         <v>11</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L14" s="6" t="s">
         <v>496</v>
@@ -4637,20 +4643,20 @@
         <v>24</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J15" s="6">
         <v>12</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L15" s="6" t="s">
         <v>496</v>
@@ -4700,20 +4706,20 @@
         <v>24</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="J16" s="6">
         <v>13</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="L16" s="6" t="s">
         <v>496</v>
@@ -4763,10 +4769,10 @@
         <v>24</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="20" t="s">
@@ -4821,10 +4827,10 @@
         <v>24</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G18" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
@@ -4879,10 +4885,10 @@
         <v>24</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
@@ -4941,11 +4947,11 @@
         <v>25</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J20" s="6">
         <v>17</v>
@@ -5000,11 +5006,11 @@
         <v>25</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="H21" s="6"/>
       <c r="I21" s="6" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="J21" s="6">
         <v>18</v>
@@ -5057,14 +5063,14 @@
         <v>24</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="G22" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="J22" s="6">
         <v>19</v>
@@ -5120,7 +5126,7 @@
         <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H23" s="6"/>
       <c r="I23" s="6" t="s">
@@ -5180,7 +5186,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H24" s="6"/>
       <c r="I24" s="6" t="s">
@@ -5237,10 +5243,10 @@
         <v>24</v>
       </c>
       <c r="F25" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G25" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H25" s="6"/>
       <c r="I25" s="6" t="s">
@@ -5256,7 +5262,7 @@
         <v>237</v>
       </c>
       <c r="M25" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N25" s="6" t="s">
         <v>338</v>
@@ -5280,7 +5286,7 @@
       <c r="W25" s="2"/>
       <c r="X25" s="2"/>
       <c r="Y25" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="Z25" s="2"/>
       <c r="AA25" s="2"/>
@@ -5297,10 +5303,10 @@
         <v>24</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="6" t="s">
@@ -5354,10 +5360,10 @@
         <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G27" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H27" s="6"/>
       <c r="I27" s="6" t="s">
@@ -5412,10 +5418,10 @@
         <v>24</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H28" s="6"/>
       <c r="I28" s="6" t="s">
@@ -5457,7 +5463,7 @@
         <v>681</v>
       </c>
       <c r="Y28" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="Z28" s="2"/>
       <c r="AA28" s="2"/>
@@ -6437,7 +6443,7 @@
   <sheetData>
     <row r="1" spans="1:26">
       <c r="A1" s="38" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B1" s="37"/>
       <c r="C1" s="37"/>
@@ -6538,10 +6544,16 @@
       <c r="G3" s="43" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
+      <c r="H3" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L3" s="43" t="s">
         <v>25</v>
       </c>
@@ -6598,10 +6610,16 @@
       <c r="G4" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="43"/>
-      <c r="J4" s="43"/>
-      <c r="K4" s="43"/>
+      <c r="H4" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L4" s="43"/>
       <c r="M4" s="43"/>
       <c r="N4" s="43" t="s">
@@ -6625,9 +6643,16 @@
       <c r="G5" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
-      <c r="J5" s="43"/>
+      <c r="H5" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L5" s="43"/>
       <c r="M5" s="43"/>
       <c r="N5" s="43" t="s">
@@ -6643,7 +6668,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" s="65" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B6" s="43"/>
       <c r="C6" s="43"/>
@@ -6651,9 +6676,16 @@
       <c r="G6" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
+      <c r="H6" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L6" s="43"/>
       <c r="M6" s="43"/>
       <c r="N6" s="43" t="s">
@@ -6669,7 +6701,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" s="65" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B7" s="43"/>
       <c r="C7" s="43"/>
@@ -6677,9 +6709,16 @@
       <c r="G7" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
-      <c r="J7" s="43"/>
+      <c r="H7" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L7" s="43"/>
       <c r="M7" s="43"/>
       <c r="N7" s="43" t="s">
@@ -6695,7 +6734,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" s="65" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B8" s="43"/>
       <c r="C8" s="43"/>
@@ -6703,9 +6742,16 @@
       <c r="G8" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="43"/>
+      <c r="H8" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J8" s="6"/>
+      <c r="K8" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L8" s="43"/>
       <c r="M8" s="43"/>
       <c r="N8" s="43" t="s">
@@ -6721,7 +6767,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" s="65" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B9" s="43"/>
       <c r="C9" s="43"/>
@@ -6729,9 +6775,16 @@
       <c r="G9" s="43" t="s">
         <v>30</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
+      <c r="H9" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>862</v>
+      </c>
+      <c r="J9" s="6"/>
+      <c r="K9" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L9" s="43"/>
       <c r="M9" s="43"/>
       <c r="N9" s="43" t="s">
@@ -6796,14 +6849,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="22">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="75" t="s">
         <v>321</v>
       </c>
-      <c r="B1" s="74"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="75"/>
+      <c r="C1" s="76" t="s">
         <v>322</v>
       </c>
-      <c r="D1" s="75"/>
+      <c r="D1" s="76"/>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
     </row>
@@ -6955,10 +7008,10 @@
         <v>24</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
@@ -6998,10 +7051,10 @@
         <v>24</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
@@ -7038,17 +7091,17 @@
         <v>24</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K6" t="s">
         <v>103</v>
@@ -7079,10 +7132,10 @@
         <v>24</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
@@ -7095,7 +7148,7 @@
         <v>237</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="M7" s="6" t="s">
         <v>338</v>
@@ -7104,7 +7157,7 @@
         <v>680</v>
       </c>
       <c r="X7" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16">
@@ -7119,10 +7172,10 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
@@ -7147,7 +7200,7 @@
         <v>341</v>
       </c>
       <c r="X8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -7155,17 +7208,17 @@
         <v>342</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C9" s="9"/>
       <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
@@ -7195,21 +7248,21 @@
         <v>343</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C10" s="9"/>
       <c r="E10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>881</v>
+        <v>862</v>
       </c>
       <c r="H10" s="9"/>
-      <c r="I10" t="s">
-        <v>882</v>
+      <c r="I10" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>651</v>
@@ -7242,32 +7295,32 @@
         <v>24</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="L11" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M11" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="X11" t="s">
         <v>782</v>
-      </c>
-      <c r="X11" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16">
@@ -7282,23 +7335,23 @@
         <v>24</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H12" s="12"/>
       <c r="I12" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>348</v>
       </c>
       <c r="L12" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="M12" s="12" t="s">
         <v>349</v>
@@ -7322,23 +7375,23 @@
         <v>24</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H13" s="12"/>
       <c r="I13" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>348</v>
       </c>
       <c r="L13" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="M13" s="12" t="s">
         <v>349</v>
@@ -7362,23 +7415,23 @@
         <v>24</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>348</v>
       </c>
       <c r="L14" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="M14" s="12" t="s">
         <v>349</v>
@@ -7402,23 +7455,23 @@
         <v>24</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>348</v>
       </c>
       <c r="L15" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="M15" s="12" t="s">
         <v>349</v>
@@ -7435,30 +7488,30 @@
         <v>50</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C16" s="9"/>
       <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>348</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="M16" s="12" t="s">
         <v>349</v>
@@ -7482,17 +7535,17 @@
         <v>25</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>103</v>
@@ -7507,7 +7560,7 @@
         <v>359</v>
       </c>
       <c r="X17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="16">
@@ -7522,10 +7575,10 @@
         <v>24</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="12" t="s">
@@ -7538,7 +7591,7 @@
         <v>652</v>
       </c>
       <c r="L18" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="M18" s="12" t="s">
         <v>98</v>
@@ -7562,23 +7615,23 @@
         <v>24</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J19" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K19" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L19" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="M19" s="12" t="s">
         <v>25</v>
@@ -7595,30 +7648,30 @@
         <v>365</v>
       </c>
       <c r="B20" s="14" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C20" s="9"/>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G20" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J20" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K20" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L20" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="M20" s="12" t="s">
         <v>25</v>
@@ -7635,30 +7688,30 @@
         <v>366</v>
       </c>
       <c r="B21" s="14" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C21" s="11"/>
       <c r="E21" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J21" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K21" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L21" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M21" s="12" t="s">
         <v>25</v>
@@ -7682,23 +7735,23 @@
         <v>24</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G22" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J22" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K22" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L22" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M22" s="12" t="s">
         <v>25</v>
@@ -7715,24 +7768,24 @@
         <v>369</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C23" s="9"/>
       <c r="E23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>496</v>
@@ -7762,36 +7815,36 @@
         <v>372</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J24" s="12" t="s">
+        <v>792</v>
+      </c>
+      <c r="K24" s="26" t="s">
         <v>793</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="L24" t="s">
         <v>794</v>
       </c>
-      <c r="L24" t="s">
-        <v>795</v>
-      </c>
       <c r="M24" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="N24" s="12" t="s">
         <v>781</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>782</v>
       </c>
       <c r="O24" s="12"/>
       <c r="W24" t="s">
         <v>373</v>
       </c>
       <c r="X24" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16">
@@ -7866,14 +7919,14 @@
         <v>24</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J26" s="12" t="s">
         <v>26</v>
@@ -8055,14 +8108,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="76" t="s">
+      <c r="A1" s="77" t="s">
         <v>380</v>
       </c>
-      <c r="B1" s="76"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="77"/>
+      <c r="C1" s="76" t="s">
         <v>381</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -8212,10 +8265,10 @@
         <v>24</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" s="9" t="s">
@@ -8255,10 +8308,10 @@
         <v>24</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9" t="s">
@@ -8295,17 +8348,17 @@
         <v>24</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J6" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K6" t="s">
         <v>103</v>
@@ -8336,10 +8389,10 @@
         <v>24</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9" t="s">
@@ -8376,10 +8429,10 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9" t="s">
@@ -8404,7 +8457,7 @@
         <v>341</v>
       </c>
       <c r="X8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -8412,17 +8465,17 @@
         <v>342</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C9" s="9"/>
       <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9" t="s">
@@ -8452,21 +8505,21 @@
         <v>343</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C10" s="9"/>
       <c r="E10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="J10" s="6" t="s">
         <v>651</v>
@@ -8499,32 +8552,32 @@
         <v>24</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J11" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="K11" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="K11" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="L11" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M11" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N11" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="X11" t="s">
         <v>782</v>
-      </c>
-      <c r="X11" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="12" spans="1:24" s="53" customFormat="1" ht="16">
@@ -8584,30 +8637,30 @@
         <v>382</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="C16" s="9"/>
       <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>348</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="M16" s="12" t="s">
         <v>349</v>
@@ -8631,17 +8684,17 @@
         <v>25</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="12" t="s">
         <v>25</v>
       </c>
       <c r="J17" s="12" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K17" s="12" t="s">
         <v>103</v>
@@ -8656,7 +8709,7 @@
         <v>359</v>
       </c>
       <c r="X17" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="18" spans="1:24" s="53" customFormat="1" ht="16">
@@ -8729,24 +8782,24 @@
         <v>383</v>
       </c>
       <c r="B23" s="14" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="C23" s="9"/>
       <c r="E23" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H23" s="12"/>
       <c r="I23" s="12" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="J23" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K23" s="12" t="s">
         <v>496</v>
@@ -8776,36 +8829,36 @@
         <v>372</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G24" s="9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="12" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="J24" s="12" t="s">
+        <v>792</v>
+      </c>
+      <c r="K24" s="26" t="s">
         <v>793</v>
       </c>
-      <c r="K24" s="26" t="s">
+      <c r="L24" t="s">
         <v>794</v>
       </c>
-      <c r="L24" t="s">
-        <v>795</v>
-      </c>
       <c r="M24" s="12" t="s">
+        <v>780</v>
+      </c>
+      <c r="N24" s="12" t="s">
         <v>781</v>
-      </c>
-      <c r="N24" s="12" t="s">
-        <v>782</v>
       </c>
       <c r="O24" s="12"/>
       <c r="W24" t="s">
         <v>373</v>
       </c>
       <c r="X24" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16">
@@ -8880,14 +8933,14 @@
         <v>24</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G26" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J26" s="12" t="s">
         <v>26</v>
@@ -9070,14 +9123,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27">
-      <c r="A1" s="78" t="s">
+      <c r="A1" s="79" t="s">
         <v>387</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="79" t="s">
+      <c r="B1" s="79"/>
+      <c r="C1" s="80" t="s">
         <v>388</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -9156,7 +9209,7 @@
     <row r="3" spans="1:24" ht="20">
       <c r="A3" s="2"/>
       <c r="B3" s="59" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>389</v>
@@ -9236,10 +9289,13 @@
         <v>24</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J4" s="43" t="s">
         <v>651</v>
@@ -9274,10 +9330,13 @@
         <v>24</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J5" t="s">
         <v>394</v>
@@ -9315,13 +9374,13 @@
         <v>24</v>
       </c>
       <c r="F6" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G6" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I6" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G6" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J6" t="s">
         <v>394</v>
@@ -9359,14 +9418,14 @@
         <v>24</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H7" s="12"/>
       <c r="I7" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J7" t="s">
         <v>402</v>
@@ -9375,7 +9434,7 @@
         <v>653</v>
       </c>
       <c r="L7" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="M7" t="s">
         <v>403</v>
@@ -9401,23 +9460,23 @@
         <v>24</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H8" s="12"/>
       <c r="I8" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="M8" t="s">
         <v>25</v>
@@ -9437,28 +9496,28 @@
         <v>406</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F9" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G9" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I9" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="G9" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>880</v>
-      </c>
       <c r="J9" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L9" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="M9" t="s">
         <v>25</v>
@@ -9478,22 +9537,22 @@
         <v>407</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E10" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F10" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G10" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I10" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="G10" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I10" s="9" t="s">
-        <v>880</v>
-      </c>
       <c r="J10" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>496</v>
@@ -9519,22 +9578,22 @@
         <v>408</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F11" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G11" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I11" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="G11" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I11" s="9" t="s">
-        <v>880</v>
-      </c>
       <c r="J11" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>496</v>
@@ -9560,28 +9619,28 @@
         <v>409</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E12" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F12" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I12" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="G12" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I12" s="9" t="s">
-        <v>880</v>
-      </c>
       <c r="J12" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K12" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L12" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="M12" t="s">
         <v>25</v>
@@ -9607,10 +9666,13 @@
         <v>24</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I13" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J13" s="24" t="s">
         <v>402</v>
@@ -9642,20 +9704,20 @@
         <v>415</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E14" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J14" t="s">
         <v>172</v>
@@ -9687,20 +9749,20 @@
         <v>417</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J15" t="s">
         <v>172</v>
@@ -9732,20 +9794,20 @@
         <v>418</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E16" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="12" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="J16" t="s">
         <v>172</v>
@@ -9777,19 +9839,19 @@
         <v>419</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F17" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G17" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I17" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G17" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J17" t="s">
         <v>172</v>
@@ -9821,19 +9883,19 @@
         <v>420</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E18" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G18" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I18" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G18" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J18" t="s">
         <v>172</v>
@@ -9865,19 +9927,19 @@
         <v>421</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F19" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I19" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G19" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J19" t="s">
         <v>172</v>
@@ -9909,19 +9971,19 @@
         <v>422</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="E20" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F20" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I20" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G20" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I20" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J20" t="s">
         <v>172</v>
@@ -9953,19 +10015,19 @@
         <v>423</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F21" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I21" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G21" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I21" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J21" t="s">
         <v>172</v>
@@ -9997,19 +10059,19 @@
         <v>424</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="E22" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F22" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G22" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I22" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G22" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I22" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J22" t="s">
         <v>172</v>
@@ -10047,10 +10109,13 @@
         <v>24</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G23" s="9" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>25</v>
       </c>
       <c r="J23" s="24" t="s">
         <v>402</v>
@@ -10082,7 +10147,7 @@
         <v>428</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C24" t="s">
         <v>25</v>
@@ -10094,14 +10159,14 @@
         <v>25</v>
       </c>
       <c r="F24" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I24" s="9" t="s">
         <v>879</v>
       </c>
-      <c r="G24" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I24" s="9" t="s">
-        <v>880</v>
-      </c>
       <c r="J24" t="s">
         <v>25</v>
       </c>
@@ -10142,7 +10207,7 @@
         <v>25</v>
       </c>
       <c r="X24" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="16">
@@ -10156,13 +10221,13 @@
         <v>24</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G25" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="I25" s="9" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="J25" t="s">
         <v>35</v>
@@ -10191,7 +10256,7 @@
         <v>432</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C26" s="27" t="s">
         <v>25</v>
@@ -10202,8 +10267,12 @@
       <c r="E26" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="F26" s="27"/>
-      <c r="G26" s="27"/>
+      <c r="F26" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="G26" s="27" t="s">
+        <v>25</v>
+      </c>
       <c r="H26" s="27" t="s">
         <v>25</v>
       </c>
@@ -10251,7 +10320,7 @@
         <v>25</v>
       </c>
       <c r="X26" s="27" t="s">
-        <v>682</v>
+        <v>896</v>
       </c>
     </row>
     <row r="27" spans="1:24" ht="16">
@@ -10259,19 +10328,19 @@
         <v>433</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F27" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G27" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I27" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G27" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I27" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J27" s="24" t="s">
         <v>35</v>
@@ -10280,7 +10349,7 @@
         <v>238</v>
       </c>
       <c r="L27" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="M27" t="s">
         <v>25</v>
@@ -10303,19 +10372,19 @@
         <v>435</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E28" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F28" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G28" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I28" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G28" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I28" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J28" s="24" t="s">
         <v>35</v>
@@ -10324,7 +10393,7 @@
         <v>238</v>
       </c>
       <c r="L28" s="25" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="M28" t="s">
         <v>25</v>
@@ -10339,7 +10408,7 @@
         <v>434</v>
       </c>
       <c r="X28" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="29" spans="1:24" ht="16">
@@ -10353,13 +10422,13 @@
         <v>24</v>
       </c>
       <c r="F29" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G29" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I29" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G29" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I29" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J29" s="24" t="s">
         <v>35</v>
@@ -10368,7 +10437,7 @@
         <v>238</v>
       </c>
       <c r="L29" s="25" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="M29" t="s">
         <v>25</v>
@@ -10383,7 +10452,7 @@
         <v>434</v>
       </c>
       <c r="X29" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="30" spans="1:24" ht="16">
@@ -10391,19 +10460,19 @@
         <v>438</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F30" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G30" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I30" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G30" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I30" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J30" s="24" t="s">
         <v>35</v>
@@ -10412,7 +10481,7 @@
         <v>238</v>
       </c>
       <c r="L30" s="25" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M30" t="s">
         <v>25</v>
@@ -10427,7 +10496,7 @@
         <v>434</v>
       </c>
       <c r="X30" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="31" spans="1:24" ht="16">
@@ -10435,19 +10504,19 @@
         <v>439</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F31" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I31" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G31" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I31" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J31" s="24" t="s">
         <v>35</v>
@@ -10456,7 +10525,7 @@
         <v>238</v>
       </c>
       <c r="L31" s="25" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="M31" t="s">
         <v>25</v>
@@ -10471,7 +10540,7 @@
         <v>434</v>
       </c>
       <c r="X31" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
     </row>
     <row r="32" spans="1:24" ht="16">
@@ -10479,19 +10548,19 @@
         <v>440</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E32" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G32" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I32" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="J32" t="s">
         <v>35</v>
@@ -10523,19 +10592,19 @@
         <v>440</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I33" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="J33" t="s">
         <v>402</v>
@@ -10567,19 +10636,19 @@
         <v>440</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="J34" s="25" t="s">
         <v>402</v>
@@ -10588,7 +10657,7 @@
         <v>653</v>
       </c>
       <c r="L34" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="M34" t="s">
         <v>403</v>
@@ -10611,13 +10680,13 @@
         <v>24</v>
       </c>
       <c r="F35" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G35" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I35" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G35" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I35" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J35" t="s">
         <v>402</v>
@@ -10626,7 +10695,7 @@
         <v>653</v>
       </c>
       <c r="L35" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="M35" t="s">
         <v>403</v>
@@ -10641,7 +10710,7 @@
         <v>444</v>
       </c>
       <c r="X35" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="36" spans="1:24" ht="16">
@@ -10649,19 +10718,19 @@
         <v>445</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="E36" s="9" t="s">
         <v>24</v>
       </c>
       <c r="F36" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="G36" s="9" t="s">
+        <v>878</v>
+      </c>
+      <c r="I36" s="9" t="s">
         <v>879</v>
-      </c>
-      <c r="G36" s="9" t="s">
-        <v>879</v>
-      </c>
-      <c r="I36" s="9" t="s">
-        <v>880</v>
       </c>
       <c r="J36" s="12" t="s">
         <v>97</v>
@@ -11118,14 +11187,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="27">
-      <c r="A1" s="80" t="s">
+      <c r="A1" s="81" t="s">
         <v>447</v>
       </c>
-      <c r="B1" s="80"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="81"/>
+      <c r="C1" s="76" t="s">
         <v>448</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -11204,7 +11273,7 @@
     <row r="3" spans="1:24" ht="20">
       <c r="A3" s="2"/>
       <c r="B3" s="59" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>389</v>
@@ -11284,10 +11353,10 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
@@ -11325,10 +11394,10 @@
         <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
@@ -11337,10 +11406,10 @@
         <v>451</v>
       </c>
       <c r="K5" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L5" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="M5" t="s">
         <v>452</v>
@@ -11349,7 +11418,7 @@
         <v>453</v>
       </c>
       <c r="O5" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P5" t="s">
         <v>25</v>
@@ -11361,10 +11430,10 @@
         <v>25</v>
       </c>
       <c r="X5" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="16">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="64">
       <c r="A6" s="17" t="s">
         <v>449</v>
       </c>
@@ -11375,23 +11444,23 @@
         <v>372</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H6" s="9"/>
-      <c r="I6" t="s">
-        <v>888</v>
+      <c r="I6" s="67" t="s">
+        <v>897</v>
       </c>
       <c r="J6" t="s">
         <v>451</v>
       </c>
       <c r="K6" t="s">
+        <v>708</v>
+      </c>
+      <c r="L6" t="s">
         <v>709</v>
-      </c>
-      <c r="L6" t="s">
-        <v>710</v>
       </c>
       <c r="M6" t="s">
         <v>452</v>
@@ -11400,7 +11469,7 @@
         <v>453</v>
       </c>
       <c r="O6" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P6" t="s">
         <v>25</v>
@@ -11427,10 +11496,10 @@
         <v>372</v>
       </c>
       <c r="F7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
@@ -11439,10 +11508,10 @@
         <v>451</v>
       </c>
       <c r="K7" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L7" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M7" t="s">
         <v>452</v>
@@ -11451,7 +11520,7 @@
         <v>453</v>
       </c>
       <c r="O7" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P7" t="s">
         <v>25</v>
@@ -11467,7 +11536,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="16">
+    <row r="8" spans="1:24" ht="64">
       <c r="A8" s="17" t="s">
         <v>456</v>
       </c>
@@ -11478,23 +11547,23 @@
         <v>372</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="H8" s="9"/>
-      <c r="I8" t="s">
-        <v>888</v>
+      <c r="I8" s="67" t="s">
+        <v>897</v>
       </c>
       <c r="J8" t="s">
         <v>451</v>
       </c>
       <c r="K8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L8" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="M8" t="s">
         <v>452</v>
@@ -11503,7 +11572,7 @@
         <v>453</v>
       </c>
       <c r="O8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P8" t="s">
         <v>25</v>
@@ -11516,7 +11585,7 @@
       </c>
       <c r="S8" s="25"/>
       <c r="X8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -11530,10 +11599,10 @@
         <v>372</v>
       </c>
       <c r="F9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" t="s">
         <v>25</v>
@@ -11542,10 +11611,10 @@
         <v>451</v>
       </c>
       <c r="K9" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L9" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="M9" t="s">
         <v>452</v>
@@ -11554,7 +11623,7 @@
         <v>453</v>
       </c>
       <c r="O9" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P9" t="s">
         <v>25</v>
@@ -11570,7 +11639,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="16">
+    <row r="10" spans="1:24" ht="64">
       <c r="A10" s="17" t="s">
         <v>460</v>
       </c>
@@ -11581,23 +11650,23 @@
         <v>372</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H10" s="9"/>
-      <c r="I10" t="s">
-        <v>888</v>
+      <c r="I10" s="67" t="s">
+        <v>897</v>
       </c>
       <c r="J10" t="s">
         <v>451</v>
       </c>
       <c r="K10" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L10" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="M10" t="s">
         <v>452</v>
@@ -11606,7 +11675,7 @@
         <v>453</v>
       </c>
       <c r="O10" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P10" t="s">
         <v>25</v>
@@ -11622,7 +11691,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="16">
+    <row r="11" spans="1:24" ht="64">
       <c r="A11" s="17" t="s">
         <v>462</v>
       </c>
@@ -11633,23 +11702,23 @@
         <v>372</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H11" s="9"/>
-      <c r="I11" t="s">
-        <v>888</v>
+      <c r="I11" s="67" t="s">
+        <v>897</v>
       </c>
       <c r="J11" t="s">
         <v>451</v>
       </c>
       <c r="K11" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L11" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="M11" t="s">
         <v>452</v>
@@ -11658,7 +11727,7 @@
         <v>453</v>
       </c>
       <c r="O11" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="P11" t="s">
         <v>25</v>
@@ -11671,7 +11740,7 @@
       </c>
       <c r="S11" s="25"/>
       <c r="X11" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16">
@@ -12066,14 +12135,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>464</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76" t="s">
         <v>465</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -12152,7 +12221,7 @@
     <row r="3" spans="1:24" ht="20">
       <c r="A3" s="2"/>
       <c r="B3" s="59" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>389</v>
@@ -12235,7 +12304,7 @@
         <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" t="s">
         <v>25</v>
@@ -12273,11 +12342,11 @@
         <v>25</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="J5" t="s">
         <v>172</v>
@@ -12295,7 +12364,7 @@
         <v>174</v>
       </c>
       <c r="X5" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="16">
@@ -12312,11 +12381,11 @@
         <v>25</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="J6" t="s">
         <v>172</v>
@@ -12351,11 +12420,11 @@
         <v>25</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="J7" t="s">
         <v>172</v>
@@ -12381,7 +12450,7 @@
         <v>472</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
@@ -12390,7 +12459,7 @@
         <v>25</v>
       </c>
       <c r="G8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
@@ -12411,7 +12480,7 @@
         <v>174</v>
       </c>
       <c r="X8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -12419,7 +12488,7 @@
         <v>473</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
@@ -12428,7 +12497,7 @@
         <v>25</v>
       </c>
       <c r="G9" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I9" t="s">
         <v>25</v>
@@ -12457,7 +12526,7 @@
         <v>474</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="E10" t="s">
         <v>24</v>
@@ -12466,7 +12535,7 @@
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I10" t="s">
         <v>25</v>
@@ -12495,7 +12564,7 @@
         <v>476</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E11" t="s">
         <v>25</v>
@@ -12504,7 +12573,7 @@
         <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I11" t="s">
         <v>25</v>
@@ -12552,7 +12621,7 @@
         <v>25</v>
       </c>
       <c r="X11" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16">
@@ -12569,11 +12638,11 @@
         <v>25</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="J12" t="s">
         <v>402</v>
@@ -12582,7 +12651,7 @@
         <v>653</v>
       </c>
       <c r="L12" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="M12" t="s">
         <v>403</v>
@@ -12591,7 +12660,7 @@
         <v>404</v>
       </c>
       <c r="W12" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="X12" t="s">
         <v>25</v>
@@ -12611,11 +12680,11 @@
         <v>25</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>881</v>
+        <v>866</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" t="s">
-        <v>888</v>
+        <v>898</v>
       </c>
       <c r="J13" s="6" t="s">
         <v>651</v>
@@ -12641,7 +12710,7 @@
         <v>432</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E14" t="s">
         <v>24</v>
@@ -12650,17 +12719,17 @@
         <v>25</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>38</v>
       </c>
       <c r="K14" s="26" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L14" s="25" t="s">
         <v>38</v>
@@ -12672,7 +12741,7 @@
         <v>38</v>
       </c>
       <c r="X14" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="16">
@@ -12680,7 +12749,7 @@
         <v>477</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="E15" t="s">
         <v>24</v>
@@ -12689,17 +12758,17 @@
         <v>25</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J15" s="25" t="s">
         <v>38</v>
       </c>
       <c r="K15" s="26" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L15" s="25" t="s">
         <v>38</v>
@@ -12711,7 +12780,7 @@
         <v>38</v>
       </c>
       <c r="X15" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="16">
@@ -12719,7 +12788,7 @@
         <v>478</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E16" t="s">
         <v>24</v>
@@ -12728,17 +12797,17 @@
         <v>25</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J16" s="25" t="s">
         <v>38</v>
       </c>
       <c r="K16" s="26" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L16" s="25" t="s">
         <v>38</v>
@@ -12750,7 +12819,7 @@
         <v>38</v>
       </c>
       <c r="X16" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="16">
@@ -12767,17 +12836,17 @@
         <v>25</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J17" s="25" t="s">
         <v>38</v>
       </c>
       <c r="K17" s="26" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L17" s="25" t="s">
         <v>38</v>
@@ -12789,7 +12858,7 @@
         <v>38</v>
       </c>
       <c r="X17" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="16">
@@ -12806,17 +12875,17 @@
         <v>25</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J18" s="25" t="s">
         <v>38</v>
       </c>
       <c r="K18" s="26" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="L18" s="25" t="s">
         <v>38</v>
@@ -12828,7 +12897,7 @@
         <v>38</v>
       </c>
       <c r="X18" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="16">
@@ -12836,7 +12905,7 @@
         <v>485</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E19" t="s">
         <v>24</v>
@@ -12845,7 +12914,7 @@
         <v>25</v>
       </c>
       <c r="G19" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I19" t="s">
         <v>25</v>
@@ -12857,7 +12926,7 @@
         <v>653</v>
       </c>
       <c r="L19" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="M19" t="s">
         <v>403</v>
@@ -12866,7 +12935,7 @@
         <v>404</v>
       </c>
       <c r="X19" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="16">
@@ -12883,7 +12952,7 @@
         <v>25</v>
       </c>
       <c r="G20" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I20" t="s">
         <v>25</v>
@@ -12895,7 +12964,7 @@
         <v>653</v>
       </c>
       <c r="L20" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="M20" t="s">
         <v>403</v>
@@ -12904,7 +12973,7 @@
         <v>404</v>
       </c>
       <c r="X20" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="16">
@@ -12921,11 +12990,11 @@
         <v>25</v>
       </c>
       <c r="G21" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H21" s="9"/>
       <c r="I21" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J21" t="s">
         <v>651</v>
@@ -12934,7 +13003,7 @@
         <v>238</v>
       </c>
       <c r="L21" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="M21" t="s">
         <v>25</v>
@@ -12943,7 +13012,7 @@
         <v>36</v>
       </c>
       <c r="X21" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="16">
@@ -12951,7 +13020,7 @@
         <v>490</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="E22" t="s">
         <v>24</v>
@@ -12960,7 +13029,7 @@
         <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I22" t="s">
         <v>25</v>
@@ -12972,7 +13041,7 @@
         <v>238</v>
       </c>
       <c r="L22" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="M22" t="s">
         <v>25</v>
@@ -13349,14 +13418,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>491</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76" t="s">
         <v>492</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
@@ -13451,7 +13520,7 @@
     <row r="3" spans="1:24" ht="16">
       <c r="A3" s="2"/>
       <c r="B3" s="57" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>493</v>
@@ -13591,7 +13660,7 @@
         <v>25</v>
       </c>
       <c r="X4" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="16">
@@ -13665,7 +13734,7 @@
         <v>25</v>
       </c>
       <c r="X5" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="16">
@@ -13739,7 +13808,7 @@
         <v>25</v>
       </c>
       <c r="X6" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="16">
@@ -13813,7 +13882,7 @@
         <v>25</v>
       </c>
       <c r="X7" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16">
@@ -13887,7 +13956,7 @@
         <v>25</v>
       </c>
       <c r="X8" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -13961,7 +14030,7 @@
         <v>25</v>
       </c>
       <c r="X9" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="10" spans="1:24" ht="16">
@@ -13969,7 +14038,7 @@
         <v>22</v>
       </c>
       <c r="B10" s="57" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="C10" s="27" t="s">
         <v>25</v>
@@ -14035,7 +14104,7 @@
         <v>25</v>
       </c>
       <c r="X10" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="11" spans="1:24" ht="16">
@@ -14052,22 +14121,22 @@
         <v>25</v>
       </c>
       <c r="G11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K11" t="s">
         <v>653</v>
       </c>
       <c r="L11" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M11" t="s">
+        <v>725</v>
+      </c>
+      <c r="N11" t="s">
         <v>726</v>
-      </c>
-      <c r="N11" t="s">
-        <v>727</v>
       </c>
       <c r="X11" t="s">
         <v>25</v>
@@ -14075,7 +14144,7 @@
     </row>
     <row r="12" spans="1:24" ht="16">
       <c r="A12" s="17" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B12" s="18" t="s">
         <v>34</v>
@@ -14144,7 +14213,7 @@
         <v>25</v>
       </c>
       <c r="X12" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="13" spans="1:24" ht="16">
@@ -14152,7 +14221,7 @@
         <v>50</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="C13" s="27" t="s">
         <v>25</v>
@@ -14218,12 +14287,12 @@
         <v>25</v>
       </c>
       <c r="X13" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="14" spans="1:24" ht="16">
       <c r="A14" s="17" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B14" s="18" t="s">
         <v>621</v>
@@ -14292,7 +14361,7 @@
         <v>25</v>
       </c>
       <c r="X14" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="16">
@@ -14366,7 +14435,7 @@
         <v>25</v>
       </c>
       <c r="X15" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="16" spans="1:24" ht="16">
@@ -14440,7 +14509,7 @@
         <v>25</v>
       </c>
       <c r="X16" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="17" spans="1:24" ht="16">
@@ -14514,7 +14583,7 @@
         <v>25</v>
       </c>
       <c r="X17" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="16">
@@ -14588,7 +14657,7 @@
         <v>25</v>
       </c>
       <c r="X18" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="16">
@@ -14662,15 +14731,15 @@
         <v>25</v>
       </c>
       <c r="X19" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="20" spans="1:24" ht="16">
       <c r="A20" s="64" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B20" s="63" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="C20" s="27" t="s">
         <v>25</v>
@@ -14736,7 +14805,7 @@
         <v>25</v>
       </c>
       <c r="X20" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="21" spans="1:24" ht="16">
@@ -14744,7 +14813,7 @@
         <v>333</v>
       </c>
       <c r="B21" s="63" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C21" s="27" t="s">
         <v>25</v>
@@ -14810,7 +14879,7 @@
         <v>25</v>
       </c>
       <c r="X21" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="22" spans="1:24" ht="16">
@@ -14821,16 +14890,19 @@
         <v>518</v>
       </c>
       <c r="E22" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F22" t="s">
         <v>25</v>
       </c>
       <c r="G22" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I22" t="s">
+        <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K22" t="s">
         <v>653</v>
@@ -14839,10 +14911,10 @@
         <v>216</v>
       </c>
       <c r="M22" t="s">
+        <v>725</v>
+      </c>
+      <c r="N22" t="s">
         <v>726</v>
-      </c>
-      <c r="N22" t="s">
-        <v>727</v>
       </c>
       <c r="X22" t="s">
         <v>25</v>
@@ -14856,16 +14928,19 @@
         <v>520</v>
       </c>
       <c r="E23" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F23" t="s">
         <v>25</v>
       </c>
       <c r="G23" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I23" t="s">
+        <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K23" t="s">
         <v>653</v>
@@ -14874,10 +14949,10 @@
         <v>647</v>
       </c>
       <c r="M23" t="s">
+        <v>725</v>
+      </c>
+      <c r="N23" t="s">
         <v>726</v>
-      </c>
-      <c r="N23" t="s">
-        <v>727</v>
       </c>
       <c r="X23" t="s">
         <v>25</v>
@@ -14891,28 +14966,31 @@
         <v>522</v>
       </c>
       <c r="E24" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F24" t="s">
         <v>25</v>
       </c>
       <c r="G24" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I24" t="s">
+        <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K24" t="s">
         <v>653</v>
       </c>
       <c r="L24" s="62" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="M24" t="s">
+        <v>725</v>
+      </c>
+      <c r="N24" t="s">
         <v>726</v>
-      </c>
-      <c r="N24" t="s">
-        <v>727</v>
       </c>
       <c r="X24" t="s">
         <v>25</v>
@@ -14926,28 +15004,31 @@
         <v>524</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F25" t="s">
         <v>25</v>
       </c>
       <c r="G25" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I25" t="s">
+        <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K25" t="s">
         <v>653</v>
       </c>
       <c r="L25" s="62" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="M25" t="s">
+        <v>725</v>
+      </c>
+      <c r="N25" t="s">
         <v>726</v>
-      </c>
-      <c r="N25" t="s">
-        <v>727</v>
       </c>
       <c r="X25" t="s">
         <v>25</v>
@@ -14961,28 +15042,31 @@
         <v>526</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F26" t="s">
         <v>25</v>
       </c>
       <c r="G26" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I26" t="s">
+        <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K26" t="s">
         <v>653</v>
       </c>
       <c r="L26" s="62" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="M26" t="s">
+        <v>725</v>
+      </c>
+      <c r="N26" t="s">
         <v>726</v>
-      </c>
-      <c r="N26" t="s">
-        <v>727</v>
       </c>
       <c r="X26" t="s">
         <v>25</v>
@@ -14996,28 +15080,31 @@
         <v>528</v>
       </c>
       <c r="E27" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F27" t="s">
         <v>25</v>
       </c>
       <c r="G27" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I27" t="s">
+        <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K27" t="s">
         <v>653</v>
       </c>
       <c r="L27" s="62" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="M27" t="s">
+        <v>725</v>
+      </c>
+      <c r="N27" t="s">
         <v>726</v>
-      </c>
-      <c r="N27" t="s">
-        <v>727</v>
       </c>
       <c r="X27" t="s">
         <v>25</v>
@@ -15031,28 +15118,31 @@
         <v>530</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F28" t="s">
         <v>25</v>
       </c>
       <c r="G28" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I28" t="s">
+        <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K28" t="s">
         <v>653</v>
       </c>
       <c r="L28" s="62" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="M28" t="s">
+        <v>725</v>
+      </c>
+      <c r="N28" t="s">
         <v>726</v>
-      </c>
-      <c r="N28" t="s">
-        <v>727</v>
       </c>
       <c r="X28" t="s">
         <v>25</v>
@@ -15066,28 +15156,31 @@
         <v>532</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F29" t="s">
         <v>25</v>
       </c>
       <c r="G29" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I29" t="s">
+        <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K29" t="s">
         <v>653</v>
       </c>
       <c r="L29" s="62" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="M29" t="s">
+        <v>725</v>
+      </c>
+      <c r="N29" t="s">
         <v>726</v>
-      </c>
-      <c r="N29" t="s">
-        <v>727</v>
       </c>
       <c r="X29" t="s">
         <v>25</v>
@@ -15101,28 +15194,31 @@
         <v>534</v>
       </c>
       <c r="E30" s="50" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F30" t="s">
         <v>25</v>
       </c>
       <c r="G30" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I30" t="s">
+        <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K30" t="s">
         <v>653</v>
       </c>
       <c r="L30" s="62" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="M30" t="s">
+        <v>725</v>
+      </c>
+      <c r="N30" t="s">
         <v>726</v>
-      </c>
-      <c r="N30" t="s">
-        <v>727</v>
       </c>
       <c r="X30" t="s">
         <v>25</v>
@@ -15142,22 +15238,25 @@
         <v>25</v>
       </c>
       <c r="G31" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I31" t="s">
+        <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K31" t="s">
         <v>653</v>
       </c>
       <c r="L31" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M31" t="s">
+        <v>725</v>
+      </c>
+      <c r="N31" t="s">
         <v>726</v>
-      </c>
-      <c r="N31" t="s">
-        <v>727</v>
       </c>
       <c r="X31" t="s">
         <v>25</v>
@@ -15177,22 +15276,25 @@
         <v>25</v>
       </c>
       <c r="G32" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="I32" t="s">
+        <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K32" t="s">
         <v>653</v>
       </c>
       <c r="L32" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M32" t="s">
+        <v>725</v>
+      </c>
+      <c r="N32" t="s">
         <v>726</v>
-      </c>
-      <c r="N32" t="s">
-        <v>727</v>
       </c>
       <c r="X32" t="s">
         <v>25</v>
@@ -15212,25 +15314,25 @@
         <v>25</v>
       </c>
       <c r="G33" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I33" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J33" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K33" t="s">
         <v>653</v>
       </c>
       <c r="L33" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M33" t="s">
+        <v>725</v>
+      </c>
+      <c r="N33" t="s">
         <v>726</v>
-      </c>
-      <c r="N33" t="s">
-        <v>727</v>
       </c>
       <c r="X33" t="s">
         <v>25</v>
@@ -15250,25 +15352,25 @@
         <v>25</v>
       </c>
       <c r="G34" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I34" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J34" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K34" t="s">
         <v>653</v>
       </c>
       <c r="L34" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="M34" t="s">
+        <v>725</v>
+      </c>
+      <c r="N34" t="s">
         <v>726</v>
-      </c>
-      <c r="N34" t="s">
-        <v>727</v>
       </c>
       <c r="X34" t="s">
         <v>25</v>
@@ -15288,25 +15390,25 @@
         <v>25</v>
       </c>
       <c r="G35" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I35" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J35" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K35" t="s">
         <v>653</v>
       </c>
       <c r="L35" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M35" t="s">
+        <v>725</v>
+      </c>
+      <c r="N35" t="s">
         <v>726</v>
-      </c>
-      <c r="N35" t="s">
-        <v>727</v>
       </c>
       <c r="X35" t="s">
         <v>25</v>
@@ -15326,25 +15428,25 @@
         <v>25</v>
       </c>
       <c r="G36" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I36" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J36" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K36" t="s">
         <v>653</v>
       </c>
       <c r="L36" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M36" t="s">
+        <v>725</v>
+      </c>
+      <c r="N36" t="s">
         <v>726</v>
-      </c>
-      <c r="N36" t="s">
-        <v>727</v>
       </c>
       <c r="X36" t="s">
         <v>25</v>
@@ -15364,25 +15466,25 @@
         <v>25</v>
       </c>
       <c r="G37" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I37" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="J37" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K37" t="s">
         <v>653</v>
       </c>
       <c r="L37" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="M37" t="s">
+        <v>725</v>
+      </c>
+      <c r="N37" t="s">
         <v>726</v>
-      </c>
-      <c r="N37" t="s">
-        <v>727</v>
       </c>
       <c r="X37" t="s">
         <v>25</v>
@@ -15459,7 +15561,7 @@
         <v>25</v>
       </c>
       <c r="X38" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="39" spans="1:24" ht="16">
@@ -15533,7 +15635,7 @@
         <v>25</v>
       </c>
       <c r="X39" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="40" spans="1:24" ht="16">
@@ -15548,7 +15650,7 @@
         <v>20</v>
       </c>
       <c r="E41" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
     </row>
     <row r="42" spans="1:24" ht="16">
@@ -15581,7 +15683,7 @@
         <v>20</v>
       </c>
       <c r="L45" s="61" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
     </row>
     <row r="46" spans="1:24" ht="16">
@@ -15590,7 +15692,7 @@
         <v>20</v>
       </c>
       <c r="L46" s="61" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
     <row r="47" spans="1:24" ht="16">
@@ -15599,7 +15701,7 @@
         <v>20</v>
       </c>
       <c r="L47" s="61" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
     <row r="48" spans="1:24" ht="16">
@@ -15608,7 +15710,7 @@
         <v>20</v>
       </c>
       <c r="L48" s="61" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="49" spans="1:12" ht="16">
@@ -15617,7 +15719,7 @@
         <v>20</v>
       </c>
       <c r="L49" s="61" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
     </row>
     <row r="50" spans="1:12" ht="16">
@@ -15626,7 +15728,7 @@
         <v>20</v>
       </c>
       <c r="L50" s="61" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
     </row>
     <row r="51" spans="1:12" ht="16">
@@ -15635,7 +15737,7 @@
         <v>20</v>
       </c>
       <c r="L51" s="61" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="52" spans="1:12" ht="16">
@@ -15644,7 +15746,7 @@
         <v>20</v>
       </c>
       <c r="L52" s="61" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="53" spans="1:12" ht="16">
@@ -15653,7 +15755,7 @@
         <v>20</v>
       </c>
       <c r="L53" s="61" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
     </row>
     <row r="54" spans="1:12" ht="16">
@@ -15786,14 +15888,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>552</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76" t="s">
         <v>553</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -15872,7 +15974,7 @@
     <row r="3" spans="1:24" ht="20">
       <c r="A3" s="2"/>
       <c r="B3" s="59" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>389</v>
@@ -16029,34 +16131,34 @@
         <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G5" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="K5" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="K5" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="L5" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M5" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N5" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="X5" t="s">
         <v>782</v>
-      </c>
-      <c r="X5" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="16">
@@ -16073,34 +16175,34 @@
         <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G6" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I6" t="s">
         <v>25</v>
       </c>
       <c r="J6" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="K6" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="K6" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="L6" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M6" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N6" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="X6" t="s">
         <v>782</v>
-      </c>
-      <c r="X6" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:24" ht="16">
@@ -16117,34 +16219,34 @@
         <v>38</v>
       </c>
       <c r="E7" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G7" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I7" t="s">
         <v>25</v>
       </c>
       <c r="J7" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="K7" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="L7" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M7" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N7" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="X7" t="s">
         <v>782</v>
-      </c>
-      <c r="X7" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="8" spans="1:24" ht="16">
@@ -16161,34 +16263,34 @@
         <v>38</v>
       </c>
       <c r="E8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="I8" t="s">
         <v>25</v>
       </c>
       <c r="J8" s="6" t="s">
+        <v>775</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>776</v>
       </c>
-      <c r="K8" s="6" t="s">
-        <v>777</v>
-      </c>
       <c r="L8" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="N8" s="6" t="s">
         <v>781</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="X8" t="s">
         <v>782</v>
-      </c>
-      <c r="X8" t="s">
-        <v>783</v>
       </c>
     </row>
     <row r="9" spans="1:24" ht="16">
@@ -16382,10 +16484,10 @@
       <c r="A1" t="s">
         <v>561</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="76" t="s">
         <v>562</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -16464,7 +16566,7 @@
     <row r="3" spans="1:24" ht="16">
       <c r="A3" s="2"/>
       <c r="B3" s="57" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>493</v>
@@ -16544,7 +16646,7 @@
         <v>24</v>
       </c>
       <c r="F4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G4" t="s">
         <v>25</v>
@@ -16582,7 +16684,7 @@
         <v>24</v>
       </c>
       <c r="F5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
@@ -16614,13 +16716,13 @@
         <v>565</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E6" t="s">
         <v>24</v>
       </c>
       <c r="F6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -16655,19 +16757,19 @@
         <v>567</v>
       </c>
       <c r="E7" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F7" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G7" t="s">
         <v>25</v>
       </c>
       <c r="I7" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J7" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K7" t="s">
         <v>653</v>
@@ -16676,10 +16778,10 @@
         <v>216</v>
       </c>
       <c r="M7" t="s">
+        <v>725</v>
+      </c>
+      <c r="N7" t="s">
         <v>726</v>
-      </c>
-      <c r="N7" t="s">
-        <v>727</v>
       </c>
       <c r="X7" t="s">
         <v>25</v>
@@ -16693,19 +16795,19 @@
         <v>569</v>
       </c>
       <c r="E8" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F8" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G8" t="s">
         <v>25</v>
       </c>
       <c r="I8" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K8" t="s">
         <v>653</v>
@@ -16714,10 +16816,10 @@
         <v>647</v>
       </c>
       <c r="M8" t="s">
+        <v>725</v>
+      </c>
+      <c r="N8" t="s">
         <v>726</v>
-      </c>
-      <c r="N8" t="s">
-        <v>727</v>
       </c>
       <c r="X8" t="s">
         <v>25</v>
@@ -16731,31 +16833,31 @@
         <v>574</v>
       </c>
       <c r="E9" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F9" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G9" t="s">
         <v>25</v>
       </c>
       <c r="I9" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J9" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K9" t="s">
         <v>653</v>
       </c>
       <c r="L9" s="61" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="M9" t="s">
+        <v>725</v>
+      </c>
+      <c r="N9" t="s">
         <v>726</v>
-      </c>
-      <c r="N9" t="s">
-        <v>727</v>
       </c>
       <c r="X9" t="s">
         <v>25</v>
@@ -16769,31 +16871,31 @@
         <v>576</v>
       </c>
       <c r="E10" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="F10" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="G10" t="s">
         <v>25</v>
       </c>
       <c r="I10" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="J10" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K10" t="s">
         <v>653</v>
       </c>
       <c r="L10" s="61" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="M10" t="s">
+        <v>725</v>
+      </c>
+      <c r="N10" t="s">
         <v>726</v>
-      </c>
-      <c r="N10" t="s">
-        <v>727</v>
       </c>
       <c r="X10" t="s">
         <v>25</v>
@@ -16807,10 +16909,10 @@
         <v>571</v>
       </c>
       <c r="E11" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="F11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G11" t="s">
         <v>25</v>
@@ -16819,19 +16921,19 @@
         <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K11" t="s">
         <v>653</v>
       </c>
       <c r="L11" s="62" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="M11" t="s">
+        <v>725</v>
+      </c>
+      <c r="N11" t="s">
         <v>726</v>
-      </c>
-      <c r="N11" t="s">
-        <v>727</v>
       </c>
       <c r="X11" t="s">
         <v>25</v>
@@ -16848,7 +16950,7 @@
         <v>594</v>
       </c>
       <c r="F12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G12" t="s">
         <v>25</v>
@@ -16857,19 +16959,19 @@
         <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K12" t="s">
         <v>653</v>
       </c>
       <c r="L12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="M12" t="s">
+        <v>725</v>
+      </c>
+      <c r="N12" t="s">
         <v>726</v>
-      </c>
-      <c r="N12" t="s">
-        <v>727</v>
       </c>
       <c r="X12" t="s">
         <v>25</v>
@@ -16886,7 +16988,7 @@
         <v>594</v>
       </c>
       <c r="F13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G13" t="s">
         <v>25</v>
@@ -16895,19 +16997,19 @@
         <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K13" t="s">
         <v>653</v>
       </c>
       <c r="L13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M13" t="s">
+        <v>725</v>
+      </c>
+      <c r="N13" t="s">
         <v>726</v>
-      </c>
-      <c r="N13" t="s">
-        <v>727</v>
       </c>
       <c r="X13" t="s">
         <v>25</v>
@@ -16924,7 +17026,7 @@
         <v>594</v>
       </c>
       <c r="F14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G14" t="s">
         <v>25</v>
@@ -16933,19 +17035,19 @@
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K14" t="s">
         <v>653</v>
       </c>
       <c r="L14" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="M14" t="s">
+        <v>725</v>
+      </c>
+      <c r="N14" t="s">
         <v>726</v>
-      </c>
-      <c r="N14" t="s">
-        <v>727</v>
       </c>
       <c r="X14" t="s">
         <v>25</v>
@@ -16962,7 +17064,7 @@
         <v>594</v>
       </c>
       <c r="F15" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G15" t="s">
         <v>25</v>
@@ -16971,19 +17073,19 @@
         <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K15" t="s">
         <v>653</v>
       </c>
       <c r="L15" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="M15" t="s">
+        <v>725</v>
+      </c>
+      <c r="N15" t="s">
         <v>726</v>
-      </c>
-      <c r="N15" t="s">
-        <v>727</v>
       </c>
       <c r="X15" t="s">
         <v>25</v>
@@ -17000,7 +17102,7 @@
         <v>594</v>
       </c>
       <c r="F16" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G16" t="s">
         <v>25</v>
@@ -17009,19 +17111,19 @@
         <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K16" t="s">
         <v>653</v>
       </c>
       <c r="L16" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="M16" t="s">
+        <v>725</v>
+      </c>
+      <c r="N16" t="s">
         <v>726</v>
-      </c>
-      <c r="N16" t="s">
-        <v>727</v>
       </c>
       <c r="X16" t="s">
         <v>25</v>
@@ -17038,7 +17140,7 @@
         <v>594</v>
       </c>
       <c r="F17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G17" t="s">
         <v>25</v>
@@ -17047,19 +17149,19 @@
         <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K17" t="s">
         <v>653</v>
       </c>
       <c r="L17" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="M17" t="s">
+        <v>725</v>
+      </c>
+      <c r="N17" t="s">
         <v>726</v>
-      </c>
-      <c r="N17" t="s">
-        <v>727</v>
       </c>
       <c r="X17" t="s">
         <v>25</v>
@@ -17339,10 +17441,10 @@
       <c r="B3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="70"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
@@ -17420,10 +17522,10 @@
       <c r="B4" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="70"/>
+      <c r="D4" s="71"/>
       <c r="E4" s="6" t="s">
         <v>22</v>
       </c>
@@ -17434,10 +17536,10 @@
         <v>24</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
@@ -17505,10 +17607,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
@@ -17574,10 +17676,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
@@ -17627,10 +17729,10 @@
       <c r="B7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="70"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="6" t="s">
         <v>41</v>
       </c>
@@ -17641,10 +17743,10 @@
         <v>24</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
@@ -17694,18 +17796,18 @@
       <c r="B8" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="71"/>
       <c r="G8" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="s">
@@ -17741,7 +17843,7 @@
         <v>136</v>
       </c>
       <c r="AA8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="16">
@@ -17759,10 +17861,10 @@
         <v>24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6" t="s">
@@ -17778,7 +17880,7 @@
         <v>238</v>
       </c>
       <c r="O9" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="P9" t="s">
         <v>139</v>
@@ -17796,7 +17898,7 @@
         <v>142</v>
       </c>
       <c r="AA9" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="16">
@@ -17806,18 +17908,18 @@
       <c r="B10" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="70"/>
+      <c r="D10" s="71"/>
       <c r="G10" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6" t="s">
@@ -17880,10 +17982,10 @@
         <v>25</v>
       </c>
       <c r="J11" t="s">
+        <v>870</v>
+      </c>
+      <c r="K11" s="66" t="s">
         <v>871</v>
-      </c>
-      <c r="K11" s="66" t="s">
-        <v>872</v>
       </c>
       <c r="L11">
         <v>8</v>
@@ -17936,12 +18038,15 @@
         <v>24</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="6"/>
+      <c r="K12" s="6" t="s">
+        <v>25</v>
+      </c>
       <c r="L12" s="33">
         <v>9</v>
       </c>
@@ -17999,10 +18104,10 @@
         <v>25</v>
       </c>
       <c r="J13" t="s">
+        <v>870</v>
+      </c>
+      <c r="K13" s="67" t="s">
         <v>871</v>
-      </c>
-      <c r="K13" s="67" t="s">
-        <v>872</v>
       </c>
       <c r="L13" s="6">
         <v>10</v>
@@ -18061,10 +18166,10 @@
         <v>25</v>
       </c>
       <c r="J14" t="s">
+        <v>870</v>
+      </c>
+      <c r="K14" s="67" t="s">
         <v>871</v>
-      </c>
-      <c r="K14" s="67" t="s">
-        <v>872</v>
       </c>
       <c r="L14" s="6">
         <v>11</v>
@@ -18123,10 +18228,10 @@
         <v>25</v>
       </c>
       <c r="J15" t="s">
+        <v>870</v>
+      </c>
+      <c r="K15" s="67" t="s">
         <v>871</v>
-      </c>
-      <c r="K15" s="67" t="s">
-        <v>872</v>
       </c>
       <c r="L15">
         <v>12</v>
@@ -18184,11 +18289,11 @@
         <v>25</v>
       </c>
       <c r="I16" s="25" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J16" s="25"/>
       <c r="K16" s="68" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="L16" s="32">
         <v>13</v>
@@ -18224,7 +18329,7 @@
         <v>153</v>
       </c>
       <c r="AA16" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="32">
@@ -18249,11 +18354,11 @@
         <v>25</v>
       </c>
       <c r="I17" s="25" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J17" s="25"/>
       <c r="K17" s="68" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="L17" s="32">
         <v>14</v>
@@ -18289,7 +18394,7 @@
         <v>153</v>
       </c>
       <c r="AA17" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="16">
@@ -18312,7 +18417,10 @@
         <v>25</v>
       </c>
       <c r="I18" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="K18" s="67" t="s">
+        <v>25</v>
       </c>
       <c r="L18" s="33">
         <v>15</v>
@@ -18363,10 +18471,13 @@
         <v>24</v>
       </c>
       <c r="H19" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I19" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="K19" s="67" t="s">
+        <v>25</v>
       </c>
       <c r="L19" s="34">
         <v>16</v>
@@ -18421,14 +18532,14 @@
         <v>24</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I20" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J20" s="6"/>
       <c r="K20" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="L20" s="32">
         <v>17</v>
@@ -18564,14 +18675,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>577</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76" t="s">
         <v>578</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="17" customHeight="1">
       <c r="A2" t="s">
@@ -18650,7 +18761,7 @@
     <row r="3" spans="1:24" ht="16">
       <c r="A3" s="2"/>
       <c r="B3" s="57" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>493</v>
@@ -18716,7 +18827,7 @@
         <v>493</v>
       </c>
       <c r="X3" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="4" spans="1:24" ht="16">
@@ -18790,7 +18901,7 @@
         <v>25</v>
       </c>
       <c r="X4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="5" spans="1:24" ht="16">
@@ -18864,7 +18975,7 @@
         <v>25</v>
       </c>
       <c r="X5" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="6" spans="1:24" ht="16">
@@ -19195,14 +19306,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>582</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76" t="s">
         <v>583</v>
       </c>
-      <c r="D1" s="77"/>
+      <c r="D1" s="78"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -19281,7 +19392,7 @@
     <row r="3" spans="1:24" ht="16">
       <c r="A3" s="2"/>
       <c r="B3" s="57" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C3" s="58" t="s">
         <v>493</v>
@@ -19361,29 +19472,29 @@
         <v>372</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J4" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K4" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L4" s="25" t="s">
+        <v>754</v>
+      </c>
+      <c r="M4" t="s">
         <v>752</v>
       </c>
-      <c r="K4" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L4" s="25" t="s">
-        <v>755</v>
-      </c>
-      <c r="M4" t="s">
+      <c r="N4" t="s">
         <v>753</v>
-      </c>
-      <c r="N4" t="s">
-        <v>754</v>
       </c>
       <c r="X4" t="s">
         <v>25</v>
@@ -19400,28 +19511,28 @@
         <v>372</v>
       </c>
       <c r="F5" t="s">
-        <v>896</v>
+        <v>862</v>
       </c>
       <c r="G5" t="s">
-        <v>896</v>
+        <v>862</v>
       </c>
       <c r="I5" t="s">
         <v>25</v>
       </c>
       <c r="J5" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="K5" s="25" t="s">
         <v>764</v>
       </c>
-      <c r="K5" s="25" t="s">
-        <v>765</v>
-      </c>
       <c r="L5" s="25" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="M5" t="s">
+        <v>752</v>
+      </c>
+      <c r="N5" t="s">
         <v>753</v>
-      </c>
-      <c r="N5" t="s">
-        <v>754</v>
       </c>
       <c r="X5" t="s">
         <v>25</v>
@@ -19438,29 +19549,29 @@
         <v>594</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J6" s="25" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="K6" s="25" t="s">
         <v>653</v>
       </c>
       <c r="L6" s="25" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="M6" t="s">
+        <v>725</v>
+      </c>
+      <c r="N6" t="s">
         <v>726</v>
-      </c>
-      <c r="N6" t="s">
-        <v>727</v>
       </c>
       <c r="X6" t="s">
         <v>25</v>
@@ -19477,29 +19588,29 @@
         <v>372</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J7" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K7" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L7" s="25" t="s">
+        <v>759</v>
+      </c>
+      <c r="M7" t="s">
         <v>752</v>
       </c>
-      <c r="K7" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L7" s="25" t="s">
-        <v>760</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>753</v>
-      </c>
-      <c r="N7" t="s">
-        <v>754</v>
       </c>
       <c r="X7" t="s">
         <v>25</v>
@@ -19516,29 +19627,29 @@
         <v>372</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J8" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K8" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L8" s="25" t="s">
+        <v>760</v>
+      </c>
+      <c r="M8" t="s">
         <v>752</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L8" s="25" t="s">
-        <v>761</v>
-      </c>
-      <c r="M8" t="s">
+      <c r="N8" t="s">
         <v>753</v>
-      </c>
-      <c r="N8" t="s">
-        <v>754</v>
       </c>
       <c r="X8" t="s">
         <v>25</v>
@@ -19555,29 +19666,29 @@
         <v>372</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J9" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K9" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L9" s="25" t="s">
+        <v>761</v>
+      </c>
+      <c r="M9" t="s">
         <v>752</v>
       </c>
-      <c r="K9" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L9" s="25" t="s">
-        <v>762</v>
-      </c>
-      <c r="M9" t="s">
+      <c r="N9" t="s">
         <v>753</v>
-      </c>
-      <c r="N9" t="s">
-        <v>754</v>
       </c>
       <c r="X9" t="s">
         <v>25</v>
@@ -19594,29 +19705,29 @@
         <v>372</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J10" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K10" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L10" s="25" t="s">
+        <v>761</v>
+      </c>
+      <c r="M10" t="s">
         <v>752</v>
       </c>
-      <c r="K10" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L10" s="25" t="s">
-        <v>762</v>
-      </c>
-      <c r="M10" t="s">
+      <c r="N10" t="s">
         <v>753</v>
-      </c>
-      <c r="N10" t="s">
-        <v>754</v>
       </c>
       <c r="X10" t="s">
         <v>25</v>
@@ -19693,7 +19804,7 @@
         <v>25</v>
       </c>
       <c r="X11" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
     </row>
     <row r="12" spans="1:24" ht="16">
@@ -19707,29 +19818,29 @@
         <v>372</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J12" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K12" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L12" s="25" t="s">
+        <v>755</v>
+      </c>
+      <c r="M12" t="s">
         <v>752</v>
       </c>
-      <c r="K12" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L12" s="25" t="s">
-        <v>756</v>
-      </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>753</v>
-      </c>
-      <c r="N12" t="s">
-        <v>754</v>
       </c>
       <c r="X12" t="s">
         <v>25</v>
@@ -19746,29 +19857,29 @@
         <v>372</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J13" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="K13" s="25" t="s">
         <v>764</v>
       </c>
-      <c r="K13" s="25" t="s">
-        <v>765</v>
-      </c>
       <c r="L13" s="25" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="M13" t="s">
+        <v>752</v>
+      </c>
+      <c r="N13" t="s">
         <v>753</v>
-      </c>
-      <c r="N13" t="s">
-        <v>754</v>
       </c>
       <c r="X13" t="s">
         <v>25</v>
@@ -19785,29 +19896,29 @@
         <v>372</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H14" s="9"/>
       <c r="I14" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J14" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K14" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L14" s="25" t="s">
+        <v>756</v>
+      </c>
+      <c r="M14" t="s">
         <v>752</v>
       </c>
-      <c r="K14" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L14" s="25" t="s">
-        <v>757</v>
-      </c>
-      <c r="M14" t="s">
+      <c r="N14" t="s">
         <v>753</v>
-      </c>
-      <c r="N14" t="s">
-        <v>754</v>
       </c>
       <c r="X14" t="s">
         <v>25</v>
@@ -19824,29 +19935,29 @@
         <v>372</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J15" s="25" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L15" s="25" t="s">
         <v>38</v>
       </c>
       <c r="M15" t="s">
+        <v>752</v>
+      </c>
+      <c r="N15" t="s">
         <v>753</v>
-      </c>
-      <c r="N15" t="s">
-        <v>754</v>
       </c>
       <c r="X15" t="s">
         <v>25</v>
@@ -19863,29 +19974,29 @@
         <v>372</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J16" s="25" t="s">
+        <v>763</v>
+      </c>
+      <c r="K16" s="25" t="s">
         <v>764</v>
       </c>
-      <c r="K16" s="25" t="s">
+      <c r="L16" s="25" t="s">
         <v>765</v>
       </c>
-      <c r="L16" s="25" t="s">
-        <v>766</v>
-      </c>
       <c r="M16" t="s">
+        <v>752</v>
+      </c>
+      <c r="N16" t="s">
         <v>753</v>
-      </c>
-      <c r="N16" t="s">
-        <v>754</v>
       </c>
       <c r="X16" t="s">
         <v>25</v>
@@ -19902,32 +20013,32 @@
         <v>372</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G17" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H17" s="9"/>
       <c r="I17" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J17" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L17" s="25" t="s">
+        <v>757</v>
+      </c>
+      <c r="M17" t="s">
         <v>752</v>
       </c>
-      <c r="K17" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L17" s="25" t="s">
-        <v>758</v>
-      </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>753</v>
       </c>
-      <c r="N17" t="s">
-        <v>754</v>
-      </c>
       <c r="X17" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="18" spans="1:24" ht="16">
@@ -19941,32 +20052,32 @@
         <v>372</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H18" s="9"/>
       <c r="I18" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J18" s="25" t="s">
+        <v>751</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>708</v>
+      </c>
+      <c r="L18" s="25" t="s">
+        <v>758</v>
+      </c>
+      <c r="M18" t="s">
         <v>752</v>
       </c>
-      <c r="K18" s="25" t="s">
-        <v>709</v>
-      </c>
-      <c r="L18" s="25" t="s">
-        <v>759</v>
-      </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>753</v>
       </c>
-      <c r="N18" t="s">
-        <v>754</v>
-      </c>
       <c r="X18" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
     </row>
     <row r="19" spans="1:24" ht="16">
@@ -19980,29 +20091,29 @@
         <v>372</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H19" s="9"/>
       <c r="I19" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J19" s="25" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="L19" s="25" t="s">
         <v>38</v>
       </c>
       <c r="M19" t="s">
+        <v>752</v>
+      </c>
+      <c r="N19" t="s">
         <v>753</v>
-      </c>
-      <c r="N19" t="s">
-        <v>754</v>
       </c>
       <c r="X19" t="s">
         <v>25</v>
@@ -20113,14 +20224,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:24" ht="16">
-      <c r="A1" s="75" t="s">
+      <c r="A1" s="76" t="s">
         <v>611</v>
       </c>
-      <c r="B1" s="75"/>
-      <c r="C1" s="75" t="s">
+      <c r="B1" s="76"/>
+      <c r="C1" s="76" t="s">
         <v>612</v>
       </c>
-      <c r="D1" s="75"/>
+      <c r="D1" s="76"/>
     </row>
     <row r="2" spans="1:24" ht="16">
       <c r="A2" t="s">
@@ -20199,7 +20310,7 @@
     <row r="3" spans="1:24" ht="20">
       <c r="A3" s="2"/>
       <c r="B3" s="59" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C3" s="60" t="s">
         <v>389</v>
@@ -20275,27 +20386,27 @@
       <c r="B4" s="14" t="s">
         <v>614</v>
       </c>
-      <c r="C4" s="81" t="s">
+      <c r="C4" s="70" t="s">
         <v>615</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H4" s="9"/>
       <c r="I4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K4" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L4" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="M4" s="12" t="s">
         <v>25</v>
@@ -20314,25 +20425,25 @@
       <c r="B5" s="14" t="s">
         <v>617</v>
       </c>
-      <c r="C5" s="81"/>
+      <c r="C5" s="70"/>
       <c r="F5" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J5" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K5" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="M5" s="12" t="s">
         <v>25</v>
@@ -20351,25 +20462,25 @@
       <c r="B6" s="14" t="s">
         <v>619</v>
       </c>
-      <c r="C6" s="81"/>
+      <c r="C6" s="70"/>
       <c r="F6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J6" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K6" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L6" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="M6" s="12" t="s">
         <v>25</v>
@@ -20388,25 +20499,25 @@
       <c r="B7" s="14" t="s">
         <v>621</v>
       </c>
-      <c r="C7" s="81"/>
+      <c r="C7" s="70"/>
       <c r="F7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J7" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K7" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L7" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="M7" s="12" t="s">
         <v>25</v>
@@ -20423,21 +20534,21 @@
         <v>622</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>822</v>
-      </c>
-      <c r="C8" s="81"/>
+        <v>821</v>
+      </c>
+      <c r="C8" s="70"/>
       <c r="F8" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J8" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K8" s="12" t="s">
         <v>496</v>
@@ -20462,18 +20573,21 @@
       <c r="B9" s="14" t="s">
         <v>624</v>
       </c>
-      <c r="C9" s="81"/>
+      <c r="C9" s="70"/>
       <c r="F9" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="G9" t="s">
+        <v>862</v>
       </c>
       <c r="J9" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K9" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L9" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="M9" s="12" t="s">
         <v>98</v>
@@ -20482,7 +20596,7 @@
         <v>99</v>
       </c>
       <c r="W9" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="X9" t="s">
         <v>25</v>
@@ -20495,25 +20609,25 @@
       <c r="B10" s="14" t="s">
         <v>626</v>
       </c>
-      <c r="C10" s="81"/>
+      <c r="C10" s="70"/>
       <c r="F10" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J10" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K10" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L10" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="M10" s="12" t="s">
         <v>98</v>
@@ -20522,7 +20636,7 @@
         <v>99</v>
       </c>
       <c r="W10" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="X10" t="s">
         <v>25</v>
@@ -20535,25 +20649,25 @@
       <c r="B11" s="14" t="s">
         <v>628</v>
       </c>
-      <c r="C11" s="81"/>
+      <c r="C11" s="70"/>
       <c r="F11" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G11" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H11" s="9"/>
       <c r="I11" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J11" s="12" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="K11" s="12" t="s">
         <v>237</v>
       </c>
       <c r="L11" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="M11" s="12" t="s">
         <v>98</v>
@@ -20562,7 +20676,7 @@
         <v>99</v>
       </c>
       <c r="W11" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="X11" t="s">
         <v>25</v>
@@ -20575,61 +20689,43 @@
       <c r="B12" s="14" t="s">
         <v>630</v>
       </c>
-      <c r="C12" s="82"/>
-      <c r="D12" s="82"/>
-      <c r="E12" s="82"/>
       <c r="F12" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H12" s="9"/>
       <c r="I12" t="s">
-        <v>888</v>
-      </c>
-      <c r="J12" s="82"/>
-      <c r="K12" s="82"/>
-      <c r="L12" s="82"/>
-      <c r="M12" s="82"/>
-      <c r="N12" s="82"/>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="82"/>
-      <c r="S12" s="82"/>
-      <c r="T12" s="82"/>
-      <c r="U12" s="82"/>
-      <c r="V12" s="82"/>
-      <c r="W12" s="82"/>
-      <c r="X12" s="82"/>
+        <v>887</v>
+      </c>
     </row>
     <row r="13" spans="1:24" ht="16">
       <c r="A13" s="2" t="s">
         <v>631</v>
       </c>
       <c r="B13" s="14" t="s">
-        <v>823</v>
-      </c>
-      <c r="C13" s="81"/>
+        <v>822</v>
+      </c>
+      <c r="C13" s="70"/>
       <c r="F13" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H13" s="9"/>
       <c r="I13" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J13" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K13" s="12" t="s">
         <v>652</v>
       </c>
       <c r="L13" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="M13" s="12" t="s">
         <v>98</v>
@@ -20648,12 +20744,15 @@
       <c r="B14" s="14" t="s">
         <v>633</v>
       </c>
-      <c r="C14" s="81"/>
+      <c r="C14" s="70"/>
       <c r="F14" t="s">
-        <v>863</v>
+        <v>862</v>
+      </c>
+      <c r="G14" t="s">
+        <v>862</v>
       </c>
       <c r="J14" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K14" s="12" t="s">
         <v>652</v>
@@ -20668,7 +20767,7 @@
         <v>99</v>
       </c>
       <c r="X14" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
     </row>
     <row r="15" spans="1:24" ht="16">
@@ -20676,27 +20775,27 @@
         <v>634</v>
       </c>
       <c r="B15" s="14" t="s">
-        <v>824</v>
-      </c>
-      <c r="C15" s="81"/>
+        <v>823</v>
+      </c>
+      <c r="C15" s="70"/>
       <c r="F15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H15" s="9"/>
       <c r="I15" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J15" s="12" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="K15" s="12" t="s">
         <v>652</v>
       </c>
       <c r="L15" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="M15" s="12" t="s">
         <v>98</v>
@@ -20715,25 +20814,25 @@
       <c r="B16" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="C16" s="81"/>
+      <c r="C16" s="70"/>
       <c r="F16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="G16" s="9" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="H16" s="9"/>
       <c r="I16" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="J16" s="12" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="K16" s="12" t="s">
         <v>496</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="M16" s="12" t="s">
         <v>25</v>
@@ -20866,10 +20965,10 @@
       <c r="B3" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="71" t="s">
+      <c r="C3" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="71"/>
+      <c r="D3" s="72"/>
       <c r="E3" s="49" t="s">
         <v>25</v>
       </c>
@@ -20944,24 +21043,24 @@
       <c r="B4" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="71" t="s">
+      <c r="C4" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="71"/>
-      <c r="E4" s="71" t="s">
+      <c r="D4" s="72"/>
+      <c r="E4" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="71" t="s">
+      <c r="F4" s="72" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J4" s="43"/>
       <c r="K4" s="43" t="s">
@@ -21022,10 +21121,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J5" s="43"/>
       <c r="K5" s="43" t="s">
@@ -21086,10 +21185,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J6" s="43"/>
       <c r="K6" s="43" t="s">
@@ -21132,24 +21231,24 @@
       <c r="B7" s="43" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="71"/>
-      <c r="E7" s="71" t="s">
+      <c r="D7" s="72"/>
+      <c r="E7" s="72" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="71" t="s">
+      <c r="F7" s="72" t="s">
         <v>42</v>
       </c>
       <c r="G7" s="43" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I7" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J7" s="43"/>
       <c r="K7" s="43" t="s">
@@ -21194,20 +21293,23 @@
       <c r="B8" s="43" t="s">
         <v>171</v>
       </c>
-      <c r="C8" s="71" t="s">
+      <c r="C8" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="71"/>
+      <c r="D8" s="72"/>
       <c r="G8" s="43" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J8" s="43"/>
+      <c r="K8" s="39" t="s">
+        <v>25</v>
+      </c>
       <c r="L8" s="39" t="s">
         <v>172</v>
       </c>
@@ -21249,20 +21351,23 @@
       <c r="B9" s="43" t="s">
         <v>147</v>
       </c>
-      <c r="C9" s="71" t="s">
+      <c r="C9" s="72" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="71"/>
+      <c r="D9" s="72"/>
       <c r="G9" s="43" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" s="43" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J9" s="43"/>
+      <c r="K9" s="39" t="s">
+        <v>25</v>
+      </c>
       <c r="L9" s="44" t="s">
         <v>172</v>
       </c>
@@ -21303,14 +21408,14 @@
         <v>24</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I10" s="43" t="s">
         <v>25</v>
       </c>
       <c r="J10" s="43"/>
       <c r="K10" s="69" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="L10" s="39" t="s">
         <v>172</v>
@@ -21367,11 +21472,11 @@
         <v>25</v>
       </c>
       <c r="I11" s="43" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J11" s="43"/>
       <c r="K11" s="69" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="L11" s="39" t="s">
         <v>197</v>
@@ -21425,14 +21530,14 @@
         <v>24</v>
       </c>
       <c r="H12" s="43" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I12" s="43" t="s">
         <v>25</v>
       </c>
       <c r="J12" s="43"/>
       <c r="K12" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="L12" s="39" t="s">
         <v>38</v>
@@ -21690,10 +21795,10 @@
       <c r="B3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="70"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
@@ -21771,24 +21876,24 @@
       <c r="B4" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70" t="s">
+      <c r="D4" s="71"/>
+      <c r="E4" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="71" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
@@ -21854,10 +21959,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
@@ -21925,10 +22030,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
@@ -21978,24 +22083,24 @@
       <c r="B7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70" t="s">
+      <c r="D7" s="71"/>
+      <c r="E7" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="71" t="s">
         <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
@@ -22045,20 +22150,20 @@
       <c r="B8" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="71"/>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="6" t="s">
@@ -22120,10 +22225,10 @@
         <v>24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="6" t="s">
@@ -22185,10 +22290,10 @@
         <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="6" t="s">
@@ -22248,10 +22353,10 @@
         <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="6" t="s">
@@ -22301,20 +22406,20 @@
       <c r="B12" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D12" s="70"/>
+      <c r="D12" s="71"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="6" t="s">
@@ -22376,10 +22481,10 @@
         <v>24</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="6" t="s">
@@ -22441,10 +22546,10 @@
         <v>24</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="2" t="s">
@@ -22484,7 +22589,7 @@
         <v>25</v>
       </c>
       <c r="AA14" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="16">
@@ -22504,10 +22609,10 @@
         <v>24</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="2" t="s">
@@ -22550,7 +22655,7 @@
         <v>208</v>
       </c>
       <c r="AA15" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="16">
@@ -22570,14 +22675,14 @@
         <v>24</v>
       </c>
       <c r="H16" s="43" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="I16" s="6" t="s">
         <v>25</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="2" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="L16" s="2">
         <v>13</v>
@@ -22622,11 +22727,11 @@
       <c r="V17" s="2"/>
     </row>
     <row r="18" spans="1:22" ht="15" customHeight="1">
-      <c r="B18" s="72" t="s">
+      <c r="B18" s="73" t="s">
         <v>184</v>
       </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
       <c r="G18" s="6"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
@@ -22641,11 +22746,11 @@
       <c r="V18" s="2"/>
     </row>
     <row r="19" spans="1:22" ht="15" customHeight="1">
-      <c r="B19" s="72" t="s">
+      <c r="B19" s="73" t="s">
         <v>162</v>
       </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
+      <c r="C19" s="73"/>
+      <c r="D19" s="73"/>
       <c r="G19" s="6"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
@@ -22660,11 +22765,11 @@
       <c r="V19" s="2"/>
     </row>
     <row r="20" spans="1:22" ht="15" customHeight="1">
-      <c r="B20" s="72" t="s">
+      <c r="B20" s="73" t="s">
         <v>122</v>
       </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
+      <c r="C20" s="73"/>
+      <c r="D20" s="73"/>
       <c r="L20" s="2">
         <v>3</v>
       </c>
@@ -22672,11 +22777,11 @@
       <c r="V20" s="2"/>
     </row>
     <row r="21" spans="1:22" ht="15" customHeight="1">
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="73" t="s">
         <v>210</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
       <c r="L21" s="2">
         <v>4</v>
       </c>
@@ -22684,11 +22789,11 @@
       <c r="V21" s="2"/>
     </row>
     <row r="22" spans="1:22" ht="15" customHeight="1">
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="73" t="s">
         <v>211</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
       <c r="L22" s="2">
         <v>5</v>
       </c>
@@ -22696,11 +22801,11 @@
       <c r="V22" s="2"/>
     </row>
     <row r="23" spans="1:22" ht="15" customHeight="1">
-      <c r="B23" s="72" t="s">
+      <c r="B23" s="73" t="s">
         <v>212</v>
       </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
+      <c r="C23" s="73"/>
+      <c r="D23" s="73"/>
       <c r="L23" s="2">
         <v>6</v>
       </c>
@@ -22708,11 +22813,11 @@
       <c r="V23" s="2"/>
     </row>
     <row r="24" spans="1:22" ht="15" customHeight="1">
-      <c r="B24" s="72" t="s">
+      <c r="B24" s="73" t="s">
         <v>168</v>
       </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
+      <c r="C24" s="73"/>
+      <c r="D24" s="73"/>
       <c r="L24" s="2">
         <v>7</v>
       </c>
@@ -22733,6 +22838,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E7:F7"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="B18:D18"/>
@@ -22741,12 +22852,6 @@
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B23:D23"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="C8:D8"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="E7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -22866,10 +22971,10 @@
       <c r="B3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="70"/>
+      <c r="D3" s="71"/>
       <c r="E3" s="4" t="s">
         <v>25</v>
       </c>
@@ -22942,29 +23047,29 @@
     </row>
     <row r="4" spans="1:27" ht="16">
       <c r="A4" s="30" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="70"/>
-      <c r="E4" s="70" t="s">
+      <c r="D4" s="71"/>
+      <c r="E4" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="71" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
@@ -23030,10 +23135,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
@@ -23097,10 +23202,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
@@ -23162,10 +23267,10 @@
         <v>24</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
@@ -23223,10 +23328,10 @@
         <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J8" s="6"/>
       <c r="K8" s="6" t="s">
@@ -23284,10 +23389,10 @@
         <v>24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J9" s="6"/>
       <c r="K9" s="6" t="s">
@@ -23345,10 +23450,10 @@
         <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J10" s="6"/>
       <c r="K10" s="6" t="s">
@@ -23364,7 +23469,7 @@
         <v>653</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="P10" s="6" t="s">
         <v>106</v>
@@ -23406,10 +23511,10 @@
         <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J11" s="6"/>
       <c r="K11" s="6" t="s">
@@ -23425,7 +23530,7 @@
         <v>653</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="P11" s="6" t="s">
         <v>106</v>
@@ -23472,7 +23577,7 @@
         <v>25</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J12" s="6"/>
       <c r="K12" s="6" t="s">
@@ -23488,7 +23593,7 @@
         <v>653</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>106</v>
@@ -23535,7 +23640,7 @@
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J13" s="6"/>
       <c r="K13" s="6" t="s">
@@ -23551,7 +23656,7 @@
         <v>653</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="P13" s="6" t="s">
         <v>106</v>
@@ -23598,7 +23703,7 @@
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
@@ -23614,7 +23719,7 @@
         <v>653</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="P14" s="6" t="s">
         <v>106</v>
@@ -23661,7 +23766,7 @@
         <v>25</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
@@ -23677,7 +23782,7 @@
         <v>653</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>106</v>
@@ -23719,10 +23824,10 @@
         <v>24</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I16" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J16" s="6"/>
       <c r="K16" s="6" t="s">
@@ -23738,7 +23843,7 @@
         <v>653</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="P16" s="6" t="s">
         <v>106</v>
@@ -23785,7 +23890,7 @@
         <v>25</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J17" s="6"/>
       <c r="K17" s="6" t="s">
@@ -23801,7 +23906,7 @@
         <v>653</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="P17" s="6" t="s">
         <v>106</v>
@@ -23843,10 +23948,10 @@
         <v>24</v>
       </c>
       <c r="H18" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I18" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J18" s="6"/>
       <c r="K18" s="6" t="s">
@@ -23862,7 +23967,7 @@
         <v>653</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="P18" s="6" t="s">
         <v>106</v>
@@ -23937,11 +24042,11 @@
       <c r="V20" s="2"/>
     </row>
     <row r="21" spans="1:27" ht="15" customHeight="1">
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="73" t="s">
         <v>228</v>
       </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
+      <c r="C21" s="73"/>
+      <c r="D21" s="73"/>
       <c r="L21" s="7">
         <v>2</v>
       </c>
@@ -23949,11 +24054,11 @@
       <c r="V21" s="2"/>
     </row>
     <row r="22" spans="1:27" ht="15" customHeight="1">
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="73" t="s">
         <v>229</v>
       </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
+      <c r="C22" s="73"/>
+      <c r="D22" s="73"/>
       <c r="L22" s="7">
         <v>3</v>
       </c>
@@ -24004,11 +24109,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="74" t="s">
         <v>230</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="16">
@@ -24171,7 +24276,7 @@
     </row>
     <row r="4" spans="1:26" ht="16">
       <c r="A4" s="30" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>206</v>
@@ -24180,20 +24285,20 @@
         <v>129</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="71" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
@@ -24256,10 +24361,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
@@ -24320,10 +24425,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
@@ -24368,24 +24473,24 @@
       <c r="B7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="70"/>
-      <c r="E7" s="70" t="s">
+      <c r="D7" s="71"/>
+      <c r="E7" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="71" t="s">
         <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
@@ -24430,18 +24535,18 @@
       <c r="B8" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="71"/>
       <c r="G8" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>25</v>
@@ -24450,7 +24555,7 @@
         <v>197</v>
       </c>
       <c r="M8" s="25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>38</v>
@@ -24466,7 +24571,7 @@
         <v>232</v>
       </c>
       <c r="Z8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="16">
@@ -24476,18 +24581,18 @@
       <c r="B9" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="70"/>
+      <c r="D9" s="71"/>
       <c r="G9" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>25</v>
@@ -24496,7 +24601,7 @@
         <v>197</v>
       </c>
       <c r="M9" s="25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>38</v>
@@ -24512,7 +24617,7 @@
         <v>232</v>
       </c>
       <c r="Z9" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="16">
@@ -24522,18 +24627,18 @@
       <c r="B10" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="C10" s="70" t="s">
+      <c r="C10" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D10" s="70"/>
+      <c r="D10" s="71"/>
       <c r="G10" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>25</v>
@@ -24542,7 +24647,7 @@
         <v>197</v>
       </c>
       <c r="M10" s="25" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>38</v>
@@ -24558,7 +24663,7 @@
         <v>232</v>
       </c>
       <c r="Z10" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="16">
@@ -24833,7 +24938,7 @@
     </row>
     <row r="4" spans="1:26" ht="16">
       <c r="A4" s="30" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>206</v>
@@ -24842,20 +24947,20 @@
         <v>129</v>
       </c>
       <c r="D4" s="6"/>
-      <c r="E4" s="70" t="s">
+      <c r="E4" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="70" t="s">
+      <c r="F4" s="71" t="s">
         <v>23</v>
       </c>
       <c r="G4" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J4" s="6"/>
       <c r="K4" s="6" t="s">
@@ -24916,10 +25021,10 @@
         <v>24</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J5" s="6"/>
       <c r="K5" s="6" t="s">
@@ -24982,10 +25087,10 @@
         <v>24</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J6" s="6"/>
       <c r="K6" s="6" t="s">
@@ -25034,20 +25139,20 @@
         <v>129</v>
       </c>
       <c r="D7" s="6"/>
-      <c r="E7" s="70" t="s">
+      <c r="E7" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="70" t="s">
+      <c r="F7" s="71" t="s">
         <v>42</v>
       </c>
       <c r="G7" s="6" t="s">
         <v>24</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="J7" s="6"/>
       <c r="K7" s="6" t="s">
@@ -25100,38 +25205,38 @@
         <v>24</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L8" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M8" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N8" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O8" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="P8" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="P8" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="Q8" s="6" t="s">
         <v>38</v>
       </c>
       <c r="T8" s="2"/>
       <c r="Y8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="16">
@@ -25149,38 +25254,38 @@
         <v>24</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N9" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O9" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="P9" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="P9" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="Q9" s="6" t="s">
         <v>38</v>
       </c>
       <c r="T9" s="2"/>
       <c r="Y9" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z9" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="16">
@@ -25198,38 +25303,38 @@
         <v>24</v>
       </c>
       <c r="H10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I10" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K10" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L10" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N10" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O10" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="P10" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="P10" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="Q10" s="6" t="s">
         <v>38</v>
       </c>
       <c r="T10" s="2"/>
       <c r="Y10" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z10" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="16">
@@ -25247,38 +25352,38 @@
         <v>24</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N11" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O11" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="P11" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="P11" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="Q11" s="6" t="s">
         <v>38</v>
       </c>
       <c r="T11" s="2"/>
       <c r="Y11" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z11" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="16">
@@ -25296,38 +25401,38 @@
         <v>24</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I12" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K12" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L12" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N12" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O12" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="P12" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="P12" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="Q12" s="6" t="s">
         <v>38</v>
       </c>
       <c r="T12" s="2"/>
       <c r="Y12" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z12" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="16">
@@ -25345,38 +25450,38 @@
         <v>24</v>
       </c>
       <c r="H13" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K13" s="6" t="s">
         <v>25</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="N13" s="6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="O13" s="6" t="s">
+        <v>780</v>
+      </c>
+      <c r="P13" s="6" t="s">
         <v>781</v>
-      </c>
-      <c r="P13" s="6" t="s">
-        <v>782</v>
       </c>
       <c r="Q13" s="6" t="s">
         <v>38</v>
       </c>
       <c r="T13" s="2"/>
       <c r="Y13" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="Z13" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="16">
@@ -25464,11 +25569,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="74" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="16">
@@ -25558,10 +25663,10 @@
       <c r="B3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="70"/>
+      <c r="D3" s="71"/>
       <c r="F3">
         <v>0</v>
       </c>
@@ -25633,10 +25738,10 @@
       <c r="B4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="70"/>
+      <c r="D4" s="71"/>
       <c r="F4">
         <v>1</v>
       </c>
@@ -25650,7 +25755,7 @@
         <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
@@ -25700,7 +25805,7 @@
         <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K5" t="s">
         <v>25</v>
@@ -25750,7 +25855,7 @@
         <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K6" t="s">
         <v>25</v>
@@ -25781,10 +25886,10 @@
       <c r="B7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="70"/>
+      <c r="D7" s="71"/>
       <c r="E7" s="6"/>
       <c r="F7">
         <v>4</v>
@@ -25799,7 +25904,7 @@
         <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
@@ -25833,10 +25938,10 @@
       <c r="B8" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="71"/>
       <c r="F8">
         <v>5</v>
       </c>
@@ -25850,7 +25955,7 @@
         <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K8" t="s">
         <v>25</v>
@@ -25881,10 +25986,10 @@
       <c r="B9" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="70"/>
+      <c r="D9" s="71"/>
       <c r="F9">
         <v>6</v>
       </c>
@@ -25898,7 +26003,7 @@
         <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K9" t="s">
         <v>25</v>
@@ -25946,7 +26051,7 @@
         <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K10" t="s">
         <v>25</v>
@@ -25994,7 +26099,7 @@
         <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K11" t="s">
         <v>25</v>
@@ -26042,7 +26147,7 @@
         <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
@@ -26090,7 +26195,7 @@
         <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
@@ -26138,7 +26243,7 @@
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
@@ -26186,7 +26291,7 @@
         <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K15" t="s">
         <v>25</v>
@@ -26234,7 +26339,7 @@
         <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -26282,7 +26387,7 @@
         <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K17" t="s">
         <v>25</v>
@@ -26330,7 +26435,7 @@
         <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K18" t="s">
         <v>25</v>
@@ -26378,7 +26483,7 @@
         <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K19" t="s">
         <v>25</v>
@@ -26426,7 +26531,7 @@
         <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -26474,7 +26579,7 @@
         <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K21" t="s">
         <v>25</v>
@@ -26522,7 +26627,7 @@
         <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K22" t="s">
         <v>25</v>
@@ -26570,7 +26675,7 @@
         <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K23" t="s">
         <v>25</v>
@@ -26618,7 +26723,7 @@
         <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K24" t="s">
         <v>25</v>
@@ -26666,7 +26771,7 @@
         <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K25" t="s">
         <v>25</v>
@@ -26714,7 +26819,7 @@
         <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K26" t="s">
         <v>25</v>
@@ -26762,7 +26867,7 @@
         <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K27" t="s">
         <v>25</v>
@@ -26810,7 +26915,7 @@
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K28" t="s">
         <v>25</v>
@@ -26858,7 +26963,7 @@
         <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K29" t="s">
         <v>25</v>
@@ -26906,7 +27011,7 @@
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K30" t="s">
         <v>25</v>
@@ -26954,7 +27059,7 @@
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K31" t="s">
         <v>25</v>
@@ -27002,7 +27107,7 @@
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K32" t="s">
         <v>25</v>
@@ -27050,7 +27155,7 @@
         <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K33" t="s">
         <v>25</v>
@@ -27098,7 +27203,7 @@
         <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K34" t="s">
         <v>25</v>
@@ -27146,7 +27251,7 @@
         <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K35" t="s">
         <v>25</v>
@@ -27194,7 +27299,7 @@
         <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K36" t="s">
         <v>25</v>
@@ -27242,7 +27347,7 @@
         <v>25</v>
       </c>
       <c r="J37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K37" t="s">
         <v>25</v>
@@ -27290,7 +27395,7 @@
         <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K38" t="s">
         <v>25</v>
@@ -27338,7 +27443,7 @@
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K39" t="s">
         <v>25</v>
@@ -27386,7 +27491,7 @@
         <v>25</v>
       </c>
       <c r="J40" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K40" t="s">
         <v>25</v>
@@ -27434,7 +27539,7 @@
         <v>25</v>
       </c>
       <c r="J41" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K41" t="s">
         <v>25</v>
@@ -27510,11 +27615,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="21">
-      <c r="A1" s="73" t="s">
+      <c r="A1" s="74" t="s">
         <v>283</v>
       </c>
-      <c r="B1" s="73"/>
-      <c r="C1" s="73"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:26" ht="16">
@@ -27604,10 +27709,10 @@
       <c r="B3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C3" s="70" t="s">
+      <c r="C3" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="70"/>
+      <c r="D3" s="71"/>
       <c r="F3">
         <v>0</v>
       </c>
@@ -27679,10 +27784,10 @@
       <c r="B4" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="C4" s="70" t="s">
+      <c r="C4" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D4" s="70"/>
+      <c r="D4" s="71"/>
       <c r="F4">
         <v>1</v>
       </c>
@@ -27696,7 +27801,7 @@
         <v>25</v>
       </c>
       <c r="J4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K4" t="s">
         <v>25</v>
@@ -27746,7 +27851,7 @@
         <v>25</v>
       </c>
       <c r="J5" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K5" t="s">
         <v>25</v>
@@ -27796,7 +27901,7 @@
         <v>25</v>
       </c>
       <c r="J6" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K6" t="s">
         <v>25</v>
@@ -27827,10 +27932,10 @@
       <c r="B7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C7" s="70" t="s">
+      <c r="C7" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D7" s="70"/>
+      <c r="D7" s="71"/>
       <c r="F7">
         <v>4</v>
       </c>
@@ -27844,7 +27949,7 @@
         <v>25</v>
       </c>
       <c r="J7" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K7" t="s">
         <v>25</v>
@@ -27875,10 +27980,10 @@
       <c r="B8" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="C8" s="70" t="s">
+      <c r="C8" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="70"/>
+      <c r="D8" s="71"/>
       <c r="F8">
         <v>5</v>
       </c>
@@ -27892,7 +27997,7 @@
         <v>25</v>
       </c>
       <c r="J8" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K8" t="s">
         <v>25</v>
@@ -27923,10 +28028,10 @@
       <c r="B9" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="70" t="s">
+      <c r="C9" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="D9" s="70"/>
+      <c r="D9" s="71"/>
       <c r="F9">
         <v>6</v>
       </c>
@@ -27940,7 +28045,7 @@
         <v>25</v>
       </c>
       <c r="J9" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K9" t="s">
         <v>25</v>
@@ -27988,7 +28093,7 @@
         <v>25</v>
       </c>
       <c r="J10" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K10" t="s">
         <v>25</v>
@@ -28036,7 +28141,7 @@
         <v>25</v>
       </c>
       <c r="J11" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K11" t="s">
         <v>25</v>
@@ -28084,7 +28189,7 @@
         <v>25</v>
       </c>
       <c r="J12" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K12" t="s">
         <v>25</v>
@@ -28132,7 +28237,7 @@
         <v>25</v>
       </c>
       <c r="J13" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K13" t="s">
         <v>25</v>
@@ -28180,7 +28285,7 @@
         <v>25</v>
       </c>
       <c r="J14" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K14" t="s">
         <v>25</v>
@@ -28228,7 +28333,7 @@
         <v>25</v>
       </c>
       <c r="J15" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K15" t="s">
         <v>25</v>
@@ -28276,7 +28381,7 @@
         <v>25</v>
       </c>
       <c r="J16" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K16" t="s">
         <v>25</v>
@@ -28324,7 +28429,7 @@
         <v>25</v>
       </c>
       <c r="J17" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K17" t="s">
         <v>25</v>
@@ -28372,7 +28477,7 @@
         <v>25</v>
       </c>
       <c r="J18" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K18" t="s">
         <v>25</v>
@@ -28420,7 +28525,7 @@
         <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K19" t="s">
         <v>25</v>
@@ -28468,7 +28573,7 @@
         <v>25</v>
       </c>
       <c r="J20" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K20" t="s">
         <v>25</v>
@@ -28516,7 +28621,7 @@
         <v>25</v>
       </c>
       <c r="J21" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K21" t="s">
         <v>25</v>
@@ -28564,7 +28669,7 @@
         <v>25</v>
       </c>
       <c r="J22" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K22" t="s">
         <v>25</v>
@@ -28612,7 +28717,7 @@
         <v>25</v>
       </c>
       <c r="J23" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K23" t="s">
         <v>25</v>
@@ -28660,7 +28765,7 @@
         <v>25</v>
       </c>
       <c r="J24" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K24" t="s">
         <v>25</v>
@@ -28708,7 +28813,7 @@
         <v>25</v>
       </c>
       <c r="J25" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K25" t="s">
         <v>25</v>
@@ -28756,7 +28861,7 @@
         <v>25</v>
       </c>
       <c r="J26" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K26" t="s">
         <v>25</v>
@@ -28804,7 +28909,7 @@
         <v>25</v>
       </c>
       <c r="J27" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K27" t="s">
         <v>25</v>
@@ -28852,7 +28957,7 @@
         <v>25</v>
       </c>
       <c r="J28" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K28" t="s">
         <v>25</v>
@@ -28900,7 +29005,7 @@
         <v>25</v>
       </c>
       <c r="J29" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K29" t="s">
         <v>25</v>
@@ -28948,7 +29053,7 @@
         <v>25</v>
       </c>
       <c r="J30" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K30" t="s">
         <v>25</v>
@@ -28996,7 +29101,7 @@
         <v>25</v>
       </c>
       <c r="J31" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K31" t="s">
         <v>25</v>
@@ -29044,7 +29149,7 @@
         <v>25</v>
       </c>
       <c r="J32" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K32" t="s">
         <v>25</v>
@@ -29092,7 +29197,7 @@
         <v>25</v>
       </c>
       <c r="J33" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K33" t="s">
         <v>25</v>
@@ -29140,7 +29245,7 @@
         <v>25</v>
       </c>
       <c r="J34" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K34" t="s">
         <v>25</v>
@@ -29188,7 +29293,7 @@
         <v>25</v>
       </c>
       <c r="J35" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K35" t="s">
         <v>25</v>
@@ -29236,7 +29341,7 @@
         <v>25</v>
       </c>
       <c r="J36" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K36" t="s">
         <v>25</v>
@@ -29284,7 +29389,7 @@
         <v>25</v>
       </c>
       <c r="J37" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K37" t="s">
         <v>25</v>
@@ -29332,7 +29437,7 @@
         <v>25</v>
       </c>
       <c r="J38" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K38" t="s">
         <v>25</v>
@@ -29380,7 +29485,7 @@
         <v>25</v>
       </c>
       <c r="J39" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K39" t="s">
         <v>25</v>
